--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Architect, Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d4408cceed11d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7cb38e105921042f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Commercial IT Sr. Data Solution Developer</t>
+          <t>Senior Architect, Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,46 +587,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a99d5e0e955f545</t>
+          <t>https://www.indeed.com/viewjob?jk=55b10352d281c7c1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Architect, Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
+          <t>https://www.indeed.com/viewjob?jk=91b0087050e37f4d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Architect, Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Angeion Group, LLC</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
+          <t>https://www.indeed.com/viewjob?jk=747c891edb77428f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d4408cceed11d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Angeion Group, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
+          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,322 +1116,322 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GHD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
+          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,137 +1441,137 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Full Stack Engineer (Python | AWS | Scalable Systems)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
+          <t>https://www.indeed.com/viewjob?jk=8677066c2054bfc1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,207 +1616,207 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,207 +1861,207 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Full Stack Developer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BAM Technologies, LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,557 +2176,557 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
+          <t>https://www.indeed.com/viewjob?jk=ce4d99e2fdf6b3ec</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,102 +2771,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Engineer/Sr Engineer, IT Software - Quality Assurance</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GHD</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3b6151531a1a35f8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Python | AWS | Scalable Systems)</t>
+          <t>Senior Engineer, Core Banking</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Nymbus, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8677066c2054bfc1</t>
+          <t>https://www.indeed.com/viewjob?jk=aba5c8bfff271f8c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Science Professional</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Future Modern</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,89 +3016,89 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad277abfee814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3107,46 +3107,46 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,172 +3191,172 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,1652 +3436,112 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Software Engineer- Martech</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>AHOLD Delhaize</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Salisbury, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineer- Martech</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>AHOLD Delhaize</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Governance Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Data Governance Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Cupertino, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Software Engineer III, Data Pipelines</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Mulligan Funding, LLC</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Full Stack Developer III</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>BAM Technologies, LLC</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce4d99e2fdf6b3ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer-Information Technology</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Cache Creek Casino Resort</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Brooks, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Covered Insurance Solutions</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – R01560920</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Brillio LLC</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, S3, Hive, MapReduce, Spark, PySpark, Snowflake, MongoDB</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d2465c192818aee</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Jackson National Life Insurance Company</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Lansing, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Molina Healthcare</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Professional, Data Analyst</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>MVP Health Care</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Schenectady, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>PAR Technology</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Software Development Engineer III</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>GM Financial</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Arlington, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Nokia</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>WesBanco Bank, Inc.</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Wheeling, WV, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer, Applications</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Basis Technologies</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Business Intelligence Architect / Developer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Navteca</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Developer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Fairfax, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Lebanon, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Applications Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Piermont Bank</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Data Platform)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Machinify</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>AI Application Developer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Slip Robotics</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>App Dev &amp; Support Engineer III</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>App Dev &amp; Support Engineer III</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Springfield, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Worcester, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Everett, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>ETL Developer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>United Nations Federal Credit Union</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Long Island City, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Angeion Group, LLC</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GHD</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GHD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Python | AWS | Scalable Systems)</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8677066c2054bfc1</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,102 +2036,102 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Developer III</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BAM Technologies, LLC</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce4d99e2fdf6b3ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Professional, Data Analyst</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MVP Health Care</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Engineer/Sr Engineer, IT Software - Quality Assurance</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=3b6151531a1a35f8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Engineer, Core Banking</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Nymbus, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=aba5c8bfff271f8c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,59 +2806,59 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software - Quality Assurance</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b6151531a1a35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer, Core Banking</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nymbus, Inc.</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba5c8bfff271f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3015,531 +3015,6 @@
         </is>
       </c>
       <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Slip Robotics</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>App Dev &amp; Support Engineer III</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>App Dev &amp; Support Engineer III</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Data Platform)</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Machinify</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>AI Application Developer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Springfield, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Worcester, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Everett, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GHD</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>GHD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
@@ -1628,20 +1628,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
@@ -1868,25 +1868,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Professional, Data Analyst</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MVP Health Care</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,69 +2516,69 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software - Quality Assurance</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b6151531a1a35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer, Core Banking</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nymbus, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba5c8bfff271f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software - Quality Assurance</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=3b6151531a1a35f8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c3a5f71283bc</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3015,6 +3015,76 @@
         </is>
       </c>
       <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Everett, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>GHD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GHD</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
@@ -1628,20 +1628,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
@@ -1868,25 +1868,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Professional, Data Analyst</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MVP Health Care</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,139 +2446,139 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c3a5f71283bc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software - Quality Assurance</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b6151531a1a35f8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software - Quality Assurance</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b6151531a1a35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c3a5f71283bc</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2945,146 +2945,6 @@
         </is>
       </c>
       <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Springfield, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Worcester, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Everett, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Architect, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cb38e105921042f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d4408cceed11d6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Architect, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b10352d281c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Architect, Data</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b0087050e37f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Architect, Data</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747c891edb77428f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d4408cceed11d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,54 +1196,54 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>GHD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack Software Engineer (Mid-Level or Senior)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GHD</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f974df4cb0027d13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Professional, Data Analyst</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MVP Health Care</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c3a5f71283bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software - Quality Assurance</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b6151531a1a35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2875,76 +2875,6 @@
         </is>
       </c>
       <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Everett, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GHD</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a5213bf0e2059fe</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Mid-Level or Senior)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f974df4cb0027d13</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,102 +2351,102 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Professional, Data Analyst</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MVP Health Care</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2770,111 +2770,6 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Worcester, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Everett, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,69 +1256,69 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
@@ -1488,20 +1488,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,54 +1791,54 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>.Net Solution Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Innocito Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=02b9ac763b0be67c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Professional, Data Analyst</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MVP Health Care</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,77 +2341,77 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2770,6 +2770,76 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Everett, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,69 +1816,69 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,29 +1886,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>.Net Solution Architect</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Innocito Technologies Pvt Ltd</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b9ac763b0be67c</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>.Net Solution Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Innocito Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=02b9ac763b0be67c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Professional, Data Analyst</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MVP Health Care</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,89 +2456,89 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2840,6 +2840,76 @@
         </is>
       </c>
       <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Everett, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -1273,25 +1273,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>AWS Architecture - Contract</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=9be7783619e1bc9c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Engineer - Contract</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=13f06a9a34997131</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,42 +1406,42 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
@@ -1453,20 +1453,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,29 +1501,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Architecture - Contract</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=9be7783619e1bc9c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>AWS Engineer - Contract</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=13f06a9a34997131</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Architecture - Contract</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be7783619e1bc9c</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AWS Engineer - Contract</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f06a9a34997131</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,104 +1816,104 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, Splunk</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,29 +1921,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>.Net Solution Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Innocito Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=02b9ac763b0be67c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>.Net Solution Architect</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Innocito Technologies Pvt Ltd</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b9ac763b0be67c</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Gen II Fund Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,99 +2446,99 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5ed1c6ce89902</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2875,41 +2875,6 @@
         </is>
       </c>
       <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,29 +1466,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Architecture - Contract</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,24 +1536,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be7783619e1bc9c</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Engineer - Contract</t>
+          <t>AWS Architecture - Contract</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f06a9a34997131</t>
+          <t>https://www.indeed.com/viewjob?jk=9be7783619e1bc9c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Engineer - Contract</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=13f06a9a34997131</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>.Net Solution Architect</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Innocito Technologies Pvt Ltd</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b9ac763b0be67c</t>
+          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>.Net Solution Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Innocito Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=02b9ac763b0be67c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gen II Fund Services</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5ed1c6ce89902</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Gen II Fund Services</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5ed1c6ce89902</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2875,6 +2875,41 @@
         </is>
       </c>
       <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>AWS Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>Northcross Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Marquette, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,77 +591,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AWS Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Northcross Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,42 +1441,42 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
@@ -1488,20 +1488,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Architecture - Contract</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be7783619e1bc9c</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Engineer - Contract</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f06a9a34997131</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Agentic AI Framework (Python, AWS)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f067cb08ee5b102</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>.Net Solution Architect</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Innocito Technologies Pvt Ltd</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b9ac763b0be67c</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Gen II Fund Services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5ed1c6ce89902</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,139 +2376,139 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gen II Fund Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5ed1c6ce89902</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2805,111 +2805,6 @@
         </is>
       </c>
       <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Worcester, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Everett, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Kubernetes Engineer</t>
+          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Northcross Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Marquette, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Spark Streaming, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
+          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Marquette, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
+          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>AWS Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>Northcross Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,77 +2131,77 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,164 +2246,164 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gen II Fund Services</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5ed1c6ce89902</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2560,251 +2560,6 @@
         </is>
       </c>
       <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Mexico, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Curana Health</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Springfield, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Worcester, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Everett, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,35 +608,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Kubernetes Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Northcross Group</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marquette, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
+          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Marquette, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
+          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>AWS Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>Northcross Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>IBM MQ System Engineer V</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Delsys Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,77 +1291,77 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,52 +1501,52 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
@@ -1558,20 +1558,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
@@ -1833,60 +1833,60 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,112 +2131,112 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2560,6 +2560,146 @@
         </is>
       </c>
       <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Springfield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Worcester, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Everett, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,35 +643,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Kubernetes Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Northcross Group</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marquette, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Marquette, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
+          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>AWS Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>Northcross Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=22f6f7ba57d40c2f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,104 +941,104 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IBM MQ System Engineer V</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Delsys Technologies</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IBM MQ System Engineer V</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>Delsys Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,94 +1266,94 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=f1820c003bebe5f2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,112 +1571,112 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Senior Data Engineer-Information Technology (Onsite)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=c213979016f2c1b9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Professional, Data Analyst</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MVP Health Care</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,15 +2691,225 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Springfield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Worcester, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Everett, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22f6f7ba57d40c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>IBM MQ System Engineer V</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Delsys Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IBM MQ System Engineer V</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Delsys Technologies</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
+          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
         </is>
       </c>
     </row>
@@ -1203,25 +1203,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
@@ -1518,52 +1518,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Software Engineer - Middleware/Integration</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c38431e7f505eb9d</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Senior Data Engineer-Information Technology (Onsite)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology (Onsite)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,42 +1966,42 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213979016f2c1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
@@ -2136,29 +2136,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Professional, Data Analyst</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MVP Health Care</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2910,6 +2910,41 @@
         </is>
       </c>
       <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IBM MQ System Engineer V</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Delsys Technologies</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
+          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IBM MQ System Engineer V</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Delsys Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=f1820c003bebe5f2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1820c003bebe5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Software Engineer - Middleware/Integration</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c38431e7f505eb9d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Middleware/Integration</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c38431e7f505eb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
@@ -1663,20 +1663,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Senior Data Engineer-Information Technology (Onsite)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology (Onsite)</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c4352fc1dbe16d</t>
         </is>
       </c>
     </row>
@@ -2393,25 +2393,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>APIGEE Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=0f865d350c566772</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2945,6 +2945,76 @@
         </is>
       </c>
       <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Everett, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Associate Data Engineer- Hyperscale- Cloud</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af157c666d12c35</t>
+          <t>https://www.indeed.com/viewjob?jk=eee1c6c65c9ef5f7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- Hyperscale- Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,94 +531,94 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee1c6c65c9ef5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d4408cceed11d6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Spark Streaming, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d4408cceed11d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Spark Streaming, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
+          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,52 +626,52 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AWS Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Northcross Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marquette, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Marquette, MI, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Kubernetes Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Northcross Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ccecd9ed22acdf</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,77 +871,77 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>IBM MQ System Engineer V</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Delsys Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
+          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IBM MQ System Engineer V</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Delsys Technologies</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
@@ -1243,82 +1243,82 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9bb650178f491a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=f1820c003bebe5f2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Senior Software Engineer - Middleware/Integration</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1820c003bebe5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c38431e7f505eb9d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Middleware/Integration</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c38431e7f505eb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer-Information Technology (Onsite)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology (Onsite)</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,77 +1851,77 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3338ab667344c2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c4352fc1dbe16d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,29 +2131,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c4352fc1dbe16d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
@@ -2428,25 +2428,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,29 +2516,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,77 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Teza Technologies</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,70 +503,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Spark Streaming, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d4408cceed11d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Spark Streaming, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
@@ -608,35 +608,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=d64ff1548d48cfe8</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,77 +731,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>IBM MQ System Engineer V</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Delsys Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
+          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IBM MQ System Engineer V</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Delsys Technologies</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SENIOR PRODUCT ARCHITECT (HYBRID)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
+          <t>https://www.indeed.com/viewjob?jk=aab12c8c52c7821a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f1820c003bebe5f2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9bb650178f491a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9bb650178f491a</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1820c003bebe5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Software Engineer - Middleware/Integration</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c38431e7f505eb9d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Middleware/Integration</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c38431e7f505eb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Full Stack Software Engineer (Mid-Level or Senior)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f974df4cb0027d13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,29 +1501,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3338ab667344c2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Architecture - Contract</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=9be7783619e1bc9c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>AWS Engineer - Contract</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=13f06a9a34997131</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology (Onsite)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,69 +1851,69 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3338ab667344c2</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c4352fc1dbe16d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Professional, Data Analyst</t>
+          <t>.Net Solution Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MVP Health Care</t>
+          <t>Innocito Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Schenectady, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
+          <t>https://www.indeed.com/viewjob?jk=02b9ac763b0be67c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>APIGEE Development Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f865d350c566772</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>APIGEE Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=0f865d350c566772</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Gen II Fund Services</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5ed1c6ce89902</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>FiveTran Administrator / Data Integration Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Everett, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,87 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior BI Consultant (Power BI) - 26-02719</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-20.xlsx
+++ b/results/job_matches_2026-03-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- Hyperscale- Cloud</t>
+          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Spark Streaming, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee1c6c65c9ef5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Spark Streaming, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,69 +556,69 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
+          <t>https://www.indeed.com/viewjob?jk=d64ff1548d48cfe8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>AWS Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Northcross Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Marquette, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d64ff1548d48cfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marquette, MI, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Kubernetes Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Northcross Group</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>Cloud Platform and Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berwyn, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IBM MQ System Engineer V</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Delsys Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac770314ea034618</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ARCHITECT (HYBRID)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aab12c8c52c7821a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,77 +1046,77 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. GenAI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, Scala, MySQL, MongoDB, NoSQL, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f37a180376834e2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1820c003bebe5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9bb650178f491a</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,77 +1291,77 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2ba2751255ad70</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Middleware/Integration</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c38431e7f505eb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=18891b949c49ef4c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Mid-Level or Senior)</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f974df4cb0027d13</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379280223ae3ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3338ab667344c2</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Software Engineer III, Data Pipelines</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Architecture - Contract</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be7783619e1bc9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Engineer - Contract</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f06a9a34997131</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,94 +1826,94 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Pipelines</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Azure Cosmos DB, ETL, ELT, dbt, MLOps, Docker</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696e0be3bf788527</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>Senior Data Engineer - Oracle DBA - OCI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69b370f0270ee30</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>.Net Solution Architect</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Innocito Technologies Pvt Ltd</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,137 +2386,137 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b9ac763b0be67c</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>APIGEE Development Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f865d350c566772</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gen II Fund Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5ed1c6ce89902</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a1f176546a9ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0628279e3946a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2875,146 +2875,6 @@
         </is>
       </c>
       <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Mexico, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Curana Health</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>
